--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.544832160844065</v>
+        <v>1.55103522613716</v>
       </c>
       <c r="D2" t="n">
-        <v>67.48937679279869</v>
+        <v>10.96702372882979</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F2" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.836838097584117</v>
+        <v>0.4609861908574191</v>
       </c>
       <c r="D3" t="n">
-        <v>55.71735141142392</v>
+        <v>9.054069604356387</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F3" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.95607890194051</v>
+        <v>6.330362821565334</v>
       </c>
       <c r="D4" t="n">
-        <v>49.22361863535798</v>
+        <v>7.998838028245672</v>
       </c>
       <c r="E4" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F4" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.21138058142861</v>
+        <v>6.046849344482149</v>
       </c>
       <c r="D5" t="n">
-        <v>37.48807298809167</v>
+        <v>6.091811860564897</v>
       </c>
       <c r="E5" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F5" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.19697431273951</v>
+        <v>5.557008325820171</v>
       </c>
       <c r="D6" t="n">
-        <v>34.39394819317168</v>
+        <v>5.589016581390398</v>
       </c>
       <c r="E6" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F6" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.11618908579221</v>
+        <v>5.868880726441234</v>
       </c>
       <c r="D7" t="n">
-        <v>36.49298694612327</v>
+        <v>5.930110378745033</v>
       </c>
       <c r="E7" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F7" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.40045316573072</v>
+        <v>5.915073639431242</v>
       </c>
       <c r="D8" t="n">
-        <v>36.4629693557199</v>
+        <v>5.925232520304484</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F8" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.01828652780321</v>
+        <v>5.202971560768022</v>
       </c>
       <c r="D9" t="n">
-        <v>30.91757470220596</v>
+        <v>5.024105889108469</v>
       </c>
       <c r="E9" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F9" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.62935915191579</v>
+        <v>5.302270862186316</v>
       </c>
       <c r="D10" t="n">
-        <v>32.54123561287604</v>
+        <v>5.287950787092357</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F10" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.1379073828015</v>
+        <v>2.947409949705245</v>
       </c>
       <c r="D11" t="n">
-        <v>17.6420499241455</v>
+        <v>2.866833112673643</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F11" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.98026847690224</v>
+        <v>2.596793627496614</v>
       </c>
       <c r="D12" t="n">
-        <v>15.65702528727536</v>
+        <v>2.544266609182245</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F12" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.85355734564112</v>
+        <v>2.576203068666683</v>
       </c>
       <c r="D13" t="n">
-        <v>17.1275210734555</v>
+        <v>2.78322217443652</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F13" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.45365331428163</v>
+        <v>3.648718663570765</v>
       </c>
       <c r="D14" t="n">
-        <v>23.82623676012682</v>
+        <v>3.871763473520608</v>
       </c>
       <c r="E14" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F14" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.39732275629672</v>
+        <v>4.452064947898217</v>
       </c>
       <c r="D15" t="n">
-        <v>27.03535609953115</v>
+        <v>4.393245366173812</v>
       </c>
       <c r="E15" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F15" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>35.95694762849437</v>
+        <v>5.843003989630335</v>
       </c>
       <c r="D16" t="n">
-        <v>37.39479703541244</v>
+        <v>6.076654518254522</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F16" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.33211170841215</v>
+        <v>4.766468152616974</v>
       </c>
       <c r="D17" t="n">
-        <v>28.88109757250749</v>
+        <v>4.693178355532468</v>
       </c>
       <c r="E17" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F17" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.62821988494505</v>
+        <v>3.51458573130357</v>
       </c>
       <c r="D18" t="n">
-        <v>21.55071455125085</v>
+        <v>3.501991114578263</v>
       </c>
       <c r="E18" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F18" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.81705067334702</v>
+        <v>7.932770734418891</v>
       </c>
       <c r="D19" t="n">
-        <v>48.38028183386271</v>
+        <v>7.86179579800269</v>
       </c>
       <c r="E19" t="n">
-        <v>11.4175095401842</v>
+        <v>1.855345300279932</v>
       </c>
       <c r="F19" t="n">
-        <v>13.53855876285537</v>
+        <v>2.200015798963997</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
